--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2518" uniqueCount="280">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,6 +260,9 @@
     <t>Vårdkontakter som matchar begäran</t>
   </si>
   <si>
+    <t>De vårdkontakter som matchar begäran.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -343,335 +346,484 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.documentId</t>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader</t>
+  </si>
+  <si>
+    <t>Innehåller basinformation om dokumentet</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.documentId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivString
+</t>
   </si>
   <si>
     <t>Vårdkontaktens identitet, unik inom källsystemet</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.sourceSystemHSAId</t>
+    <t>Vårdkontaktens identitet som är unik inom källsystemet. Identifieraren ska vara konsistent och beständigt mellan olika majorversioner av ett kontrakt. Ett exempel på detta är att en vårdkontakt ska ha samma identifierare i majorversion 3 och 4 av ett tjänstekontrakt för att läsa vårdkontakter. Identifieraren ska vara konsistent och beständigt mellan olika kontrakt. Ett exempel på detta är att samma remiss-identitet ska användas i ett tjänstekontrakt för att läsa remisser, samt tjänstekontraktet som läser remissvar som refererar till den ursprungliga remissen.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.sourceSystemHSAId</t>
   </si>
   <si>
     <t>HSA-id för källsystemet</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.patientId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
+    <t>HSA-id för det system som dokumentet är skapat i.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.documentTitle</t>
+  </si>
+  <si>
+    <t>Titel (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetCareContacts skickar inte documentTitle. Elementet är 0..0 per TKB.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.documentTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimeStamp
 </t>
   </si>
   <si>
+    <t>Tidpunkt (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetCareContacts skickar inte documentTime. Elementet är 0..0 per TKB.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.patientId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivPersonIdTypeLogisticsLogistics3
+</t>
+  </si>
+  <si>
     <t>Patientens identifierare (personnummer/samordningsnummer)</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional</t>
+    <t>Id för patienten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional</t>
   </si>
   <si>
     <t>Ansvarig hälso- och sjukvårdspersonal</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.authorTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Hälso- och sjukvårdspersonalen som ansvarar för vårdkontakten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.authorTime</t>
+  </si>
+  <si>
+    <t>Tidpunkt då informationen registrerades (YYYYMMDDhhmmss)</t>
+  </si>
+  <si>
+    <t>Tidpunkt då informationen registrerades. Regel: Regel 2
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för ansvarig personal</t>
+  </si>
+  <si>
+    <t>HSA-id för hälso- och sjukvårdspersonal som ansvar för vårdkontakten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalName</t>
+  </si>
+  <si>
+    <t>Namn på ansvarig personal</t>
+  </si>
+  <si>
+    <t>Namn på hälso- och sjukvårdspersonal.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivCVTypeLogisticsLogistics3
 </t>
   </si>
   <si>
-    <t>Tidpunkt då informationen registrerades (YYYYMMDDhhmmss)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för ansvarig personal</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalName</t>
-  </si>
-  <si>
-    <t>Namn på ansvarig personal</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>Befattning (KV Befattning OID 1.2.752.129.2.2.1.4)</t>
+  </si>
+  <si>
+    <t>Information om hälso- och sjukvårdspersonalens befattning. Om möjligt ska KV Befattning (OID 1.2.752.129.2.2.1.4) användas. Se referens [R6].</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
+  </si>
+  <si>
+    <t>Organisationsenhet för ansvarig personal (Regel 4)</t>
+  </si>
+  <si>
+    <t>Den organisation som hälso- och sjukvårdspersonen är uppdragstagare på. Regel: Regel 4</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för org.enhet</t>
+  </si>
+  <si>
+    <t>HSA-id för organisationsenhet. Regel: Regel 4</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
+  </si>
+  <si>
+    <t>Namn på org.enhet</t>
+  </si>
+  <si>
+    <t>Namnet på den organisation som den ansvariga hälso- och sjukvårdspersonalen är uppdragstagare på. Regel: Regel 4</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
+  </si>
+  <si>
+    <t>Telefon till org.enhet</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
+  </si>
+  <si>
+    <t>E-post till org.enhet</t>
+  </si>
+  <si>
+    <t>Epost till enhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
+  </si>
+  <si>
+    <t>Postadress för org.enhet</t>
+  </si>
+  <si>
+    <t>Postadress för den organisation som hälso- och sjukvårdspersonal en är uppdragstagare på. Skrivs på ett så naturligt sätt som möjligt, exempelvis: ”Storgatan 12 468 91 Lilleby”</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
+  </si>
+  <si>
+    <t>Plats för org.enhet</t>
+  </si>
+  <si>
+    <t>Text som anger namnet på plats eller ort för organisationens fysiska placering.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdenhet (Regel 1: PDL/Sparr)</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdenhet. Regel: Regel 1</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdgivare (Regel 1: PDL/Sparr)</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdgivaren, som är vårdgivare för den enhet som hälso- och sjukvårdspersonalen är uppdragstagare för. Regel :Regel 1</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>Signering (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetCareContacts skickar inte legalAuthenticator. Elementet är 0..0 per TKB.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.legalAuthenticator.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.legalAuthenticator.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.legalAuthenticator.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.legalAuthenticator.signatureTime</t>
+  </si>
+  <si>
+    <t>signatureTime</t>
+  </si>
+  <si>
+    <t>Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.legalAuthenticator.legalAuthenticatorHSAId</t>
+  </si>
+  <si>
+    <t>legalAuthenticatorHSAId</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.legalAuthenticator.legalAuthenticatorName</t>
+  </si>
+  <si>
+    <t>legalAuthenticatorName</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.approvedForPatient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBoolean
 </t>
   </si>
   <si>
-    <t>Befattning (KV Befattning OID 1.2.752.129.2.2.1.4)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
-  </si>
-  <si>
-    <t>Organisationsenhet för ansvarig personal (Regel 4)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för org.enhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
-  </si>
-  <si>
-    <t>Namn på org.enhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
-  </si>
-  <si>
-    <t>Telefon till org.enhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
-  </si>
-  <si>
-    <t>E-post till org.enhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
-  </si>
-  <si>
-    <t>Postadress för org.enhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
-  </si>
-  <si>
-    <t>Plats för org.enhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för vårdenhet (Regel 1: PDL/Sparr)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för vårdgivare (Regel 1: PDL/Sparr)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.approvedForPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
+    <t>Informationen godkänd för patient (Regel 3)</t>
+  </si>
+  <si>
+    <t>Anger om information får delas till patient. Värdet sätts i sådant fall till true, i annat fall till false. Regel: Regel 3</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.nullified</t>
+  </si>
+  <si>
+    <t>Makulerat (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetCareContacts stödjer inte nullified. Elementet är 0..0 per TKB.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.nullifiedReason</t>
+  </si>
+  <si>
+    <t>Makuleringsskäl (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetCareContacts stödjer inte nullifiedReason. Elementet är 0..0 per TKB.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactHeader.careContactId</t>
+  </si>
+  <si>
+    <t>Vårdkontakts-id i header (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — careContactId i PatientSummaryHeader är 0..0 per TKB för GetCareContacts.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody</t>
+  </si>
+  <si>
+    <t>careContactBody</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactCode</t>
+  </si>
+  <si>
+    <t>Typ av vårdkontakt (KV Vårdkontakttyp OID 1.2.752.129.2.2.2.x)</t>
+  </si>
+  <si>
+    <t>Kod som anger på vilket sätt vårdkontakten är planerad att ske, alternativt skedde. KV Vårdkontakttyp (1.2.752.129.2.2.2.25) ska användas. Se referens [R6]. Utelämnat värde betyder att värdet är okänt.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactReason</t>
+  </si>
+  <si>
+    <t>Orsak till vårdkontakt (fri text från patient/företrädare)</t>
+  </si>
+  <si>
+    <t>Text som beskriver orsaken till vårdkontakt som patienten själv eller dess företrädare anger.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit</t>
+  </si>
+  <si>
+    <t>Enhet för vårdkontakten (Regel 5: krävs för NPÖ)</t>
+  </si>
+  <si>
+    <t>Den enhet som vårdkontakten utfördes vid eller planeras utföras vid. Regel: Regel 5</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.orgUnitHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för kontaktenhet</t>
+  </si>
+  <si>
+    <t>HSA-id för organisationsenhet. Regel: Regel 5</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.orgUnitName</t>
+  </si>
+  <si>
+    <t>Namn på kontaktenhet</t>
+  </si>
+  <si>
+    <t>Namn på organisationsenheten. Regel: Regel 5</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.orgUnitTelecom</t>
+  </si>
+  <si>
+    <t>Telefon till kontaktenhet</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenheten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.orgUnitEmail</t>
+  </si>
+  <si>
+    <t>E-post till kontaktenhet</t>
+  </si>
+  <si>
+    <t>Epost till organisationsenheten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.orgUnitAddress</t>
+  </si>
+  <si>
+    <t>Adress till kontaktenhet</t>
+  </si>
+  <si>
+    <t>Postadress till organisationsenheten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactOrgUnit.orgUnitLocation</t>
+  </si>
+  <si>
+    <t>Plats för kontaktenhet</t>
+  </si>
+  <si>
+    <t>Text som anger namnet på plats eller ort för organisationsenhetens eller funktionens fysiska placering.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactTimePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimePeriodTypeLogisticsLogistics3
 </t>
   </si>
   <si>
-    <t>Informationen godkänd för patient (Regel 3)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.documentTitle</t>
-  </si>
-  <si>
-    <t>Titel (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetCareContacts skickar inte documentTitle. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.documentTime</t>
-  </si>
-  <si>
-    <t>Tidpunkt (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetCareContacts skickar inte documentTime. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>Signering (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetCareContacts skickar inte legalAuthenticator. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.nullified</t>
-  </si>
-  <si>
-    <t>Makulerat (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetCareContacts stödjer inte nullified. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.nullifiedReason</t>
-  </si>
-  <si>
-    <t>Makuleringsskäl (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetCareContacts stödjer inte nullifiedReason. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactId</t>
-  </si>
-  <si>
-    <t>Vårdkontakts-id i header (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — careContactId i PatientSummaryHeader är 0..0 per TKB för GetCareContacts.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactCode</t>
-  </si>
-  <si>
-    <t>Typ av vårdkontakt (KV Vårdkontakttyp OID 1.2.752.129.2.2.2.x)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactReason</t>
-  </si>
-  <si>
-    <t>Orsak till vårdkontakt (fri text från patient/företrädare)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit</t>
-  </si>
-  <si>
-    <t>Enhet för vårdkontakten (Regel 5: krävs för NPÖ)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.orgUnitHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för kontaktenhet (Regel 4: obligatorisk för NPÖ)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.orgUnitName</t>
-  </si>
-  <si>
-    <t>Namn på kontaktenhet (Regel 4: obligatorisk för NPÖ)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.orgUnitTelecom</t>
-  </si>
-  <si>
-    <t>Telefon till kontaktenhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.orgUnitEmail</t>
-  </si>
-  <si>
-    <t>E-post till kontaktenhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.orgUnitAddress</t>
-  </si>
-  <si>
-    <t>Adress till kontaktenhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactOrgUnit.orgUnitLocation</t>
-  </si>
-  <si>
-    <t>Plats för kontaktenhet</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactTimePeriod</t>
-  </si>
-  <si>
     <t>Tidsintervall för vårdkontakten. Villkor: Minst ett av start och end måste anges.</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactTimePeriod.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactTimePeriod.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactTimePeriod.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactTimePeriod.start</t>
-  </si>
-  <si>
-    <t>Starttidpunkt (YYYYMMDDhhmmss)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactTimePeriod.end</t>
-  </si>
-  <si>
-    <t>Sluttidpunkt (YYYYMMDDhhmmss)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.careContactStatus</t>
+    <t>Tidsintervall för vårdkontakt. Vid besök i öppenvård sätts careContactTimePeriod.start och careContactTimePeriod.end till samma tidpunkt (besökets startidpunkt).</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.careContactStatus</t>
   </si>
   <si>
     <t>Status för vårdkontakten (SNOMED CT SE, OID 1.2.752.116.2.1.1, SCTID 53761000052103)</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.additionalPatientInformation</t>
+    <t>Kod som anger aktuell status för vårdkontakten. Kodverket är definierat i SNOMED CT-SE med SCTID: 53761000052103 (Snomed CT finns tillgängligt via R11 där man kan se de publicerade koderna som är refererade)</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.additionalPatientInformation</t>
   </si>
   <si>
     <t>Ytterligare patientinformation</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.additionalPatientInformation.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.additionalPatientInformation.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.additionalPatientInformation.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCareContacts.careContact.additionalPatientInformation.dateOfBirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date
+    <t>Ytterligare information om patienten som inte går att få tag på via en gemensam PU-slagning.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.additionalPatientInformation.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.additionalPatientInformation.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.additionalPatientInformation.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.additionalPatientInformation.dateOfBirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivPartialDateTypeLogisticsLogistics3
 </t>
   </si>
   <si>
     <t>Patientens födelsedatum (YYYY / YYYYMM / YYYYMMDD)</t>
   </si>
   <si>
-    <t>SEEHDSLMCareContacts.careContact.additionalPatientInformation.gender</t>
+    <t>Patientens födelsedatum.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareContacts.careContact.careContactBody.additionalPatientInformation.gender</t>
   </si>
   <si>
     <t>Patientens kön (KV Kön OID 1.2.752.129.2.2.1.1)</t>
   </si>
   <si>
+    <t>Patientens kön. KV Kön (1.2.752.129.2.2.1.1) bör användas. Se referens [R6].
+Enligt TKB i detta sammanhang: code 1..1, codeSystem 1..1, displayName 1..1, originalText 0..0.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCareContacts.result</t>
   </si>
   <si>
     <t>Resultatkod för anropet</t>
   </si>
   <si>
+    <t>Innehåller information om begäran gick bra eller ej.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCareContacts.result.id</t>
   </si>
   <si>
@@ -684,35 +836,48 @@
     <t>SEEHDSLMCareContacts.result.resultCode</t>
   </si>
   <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
     <t>Resultatkod: OK, INFO eller ERROR</t>
   </si>
   <si>
+    <t>Kan endast vara OK, INFO eller ERROR
+Tillåtna värden enligt XSD: OK, ERROR, INFO.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCareContacts.result.errorCode</t>
   </si>
   <si>
     <t>Felkod vid ERROR (INVALID_REQUEST)</t>
   </si>
   <si>
+    <t>Sätts endast om resultCode är ERROR, se kapitel 4.4 för mer information.
+Tillåtna värden enligt XSD: INVALID_REQUEST.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCareContacts.result.logId</t>
   </si>
   <si>
     <t>UUID för felsökning</t>
   </si>
   <si>
+    <t>En UUID som kan användas vid felanmälan för att användas vid felsökning av producent.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCareContacts.result.subCode</t>
   </si>
   <si>
     <t>Subkod</t>
   </si>
   <si>
+    <t>Inga subkoder är specificerade.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCareContacts.result.message</t>
   </si>
   <si>
     <t>Beskrivande meddelande (svenska)</t>
+  </si>
+  <si>
+    <t>En beskrivande text som kan visas för användaren.</t>
   </si>
 </sst>
 </file>
@@ -1014,11 +1179,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ70"/>
+  <dimension ref="A1:AJ79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="97.6484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="97.6484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="113.4296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="113.4296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1027,7 +1192,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="76.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1048,7 +1213,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="95.89453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="111.67578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1298,7 +1463,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1361,15 +1526,15 @@
         <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1380,7 +1545,7 @@
         <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1392,13 +1557,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1449,13 +1614,13 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1466,14 +1631,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -1492,16 +1657,16 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1539,19 +1704,19 @@
         <v>72</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1563,19 +1728,19 @@
         <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1588,25 +1753,25 @@
         <v>72</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>72</v>
@@ -1655,7 +1820,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1667,15 +1832,15 @@
         <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1683,10 +1848,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1698,13 +1863,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1755,27 +1920,27 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1783,10 +1948,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
@@ -1798,13 +1963,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1855,13 +2020,13 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>72</v>
@@ -1879,14 +2044,14 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>72</v>
@@ -1898,15 +2063,17 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>72</v>
@@ -1943,71 +2110,75 @@
         <v>72</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>72</v>
       </c>
@@ -2055,27 +2226,27 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2083,10 +2254,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>72</v>
@@ -2098,13 +2269,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2155,13 +2326,13 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>72</v>
@@ -2179,14 +2350,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
@@ -2198,17 +2369,15 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>72</v>
@@ -2245,75 +2414,71 @@
         <v>72</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>72</v>
       </c>
@@ -2361,27 +2526,27 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2389,10 +2554,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
@@ -2404,13 +2569,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2461,13 +2626,13 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
@@ -2478,10 +2643,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2489,10 +2654,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
@@ -2504,13 +2669,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2561,13 +2726,13 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
@@ -2578,10 +2743,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2589,10 +2754,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -2604,13 +2769,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2661,27 +2826,27 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2692,7 +2857,7 @@
         <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>72</v>
@@ -2704,13 +2869,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2761,13 +2926,13 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>72</v>
@@ -2778,21 +2943,21 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>72</v>
@@ -2804,15 +2969,17 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>72</v>
@@ -2849,71 +3016,75 @@
         <v>72</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>72</v>
       </c>
@@ -2961,38 +3132,38 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>72</v>
@@ -3004,17 +3175,15 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>72</v>
@@ -3051,75 +3220,71 @@
         <v>72</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>72</v>
       </c>
@@ -3167,27 +3332,27 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3198,7 +3363,7 @@
         <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>72</v>
@@ -3210,13 +3375,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3267,13 +3432,13 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>72</v>
@@ -3284,10 +3449,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3298,7 +3463,7 @@
         <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>72</v>
@@ -3310,13 +3475,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3367,13 +3532,13 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>72</v>
@@ -3384,10 +3549,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3398,7 +3563,7 @@
         <v>73</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>72</v>
@@ -3410,13 +3575,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3467,27 +3632,27 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3498,7 +3663,7 @@
         <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>72</v>
@@ -3510,13 +3675,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3567,13 +3732,13 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>72</v>
@@ -3584,21 +3749,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>72</v>
@@ -3610,15 +3775,17 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>72</v>
@@ -3655,71 +3822,75 @@
         <v>72</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>72</v>
       </c>
@@ -3767,27 +3938,27 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3798,7 +3969,7 @@
         <v>73</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>72</v>
@@ -3810,13 +3981,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3867,13 +4038,13 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>72</v>
@@ -3884,10 +4055,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3898,7 +4069,7 @@
         <v>73</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>72</v>
@@ -3910,13 +4081,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3967,13 +4138,13 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>72</v>
@@ -3984,10 +4155,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3995,10 +4166,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>72</v>
@@ -4010,13 +4181,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4067,13 +4238,13 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>72</v>
@@ -4084,10 +4255,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4098,7 +4269,7 @@
         <v>73</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>72</v>
@@ -4110,13 +4281,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4167,13 +4338,13 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>72</v>
@@ -4184,10 +4355,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4198,7 +4369,7 @@
         <v>73</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>72</v>
@@ -4210,13 +4381,13 @@
         <v>72</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4267,13 +4438,13 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>72</v>
@@ -4284,10 +4455,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4298,7 +4469,7 @@
         <v>73</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>72</v>
@@ -4310,13 +4481,13 @@
         <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4367,13 +4538,13 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>72</v>
@@ -4384,10 +4555,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4398,7 +4569,7 @@
         <v>73</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>72</v>
@@ -4410,13 +4581,13 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4467,13 +4638,13 @@
         <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>72</v>
@@ -4484,10 +4655,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4498,7 +4669,7 @@
         <v>73</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>72</v>
@@ -4510,13 +4681,13 @@
         <v>72</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4567,13 +4738,13 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>72</v>
@@ -4584,10 +4755,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4610,13 +4781,13 @@
         <v>72</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4667,7 +4838,7 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -4679,15 +4850,15 @@
         <v>72</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4698,7 +4869,7 @@
         <v>73</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>72</v>
@@ -4710,13 +4881,13 @@
         <v>72</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4767,13 +4938,13 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>169</v>
+        <v>87</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>72</v>
@@ -4784,21 +4955,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>72</v>
@@ -4810,15 +4981,17 @@
         <v>72</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>72</v>
@@ -4855,71 +5028,75 @@
         <v>72</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>72</v>
       </c>
@@ -4967,27 +5144,27 @@
         <v>72</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4995,10 +5172,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>72</v>
@@ -5010,13 +5187,13 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5067,13 +5244,13 @@
         <v>72</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>72</v>
@@ -5084,21 +5261,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>72</v>
@@ -5110,17 +5287,15 @@
         <v>72</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>72</v>
@@ -5157,75 +5332,71 @@
         <v>72</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>72</v>
       </c>
@@ -5273,27 +5444,27 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5301,10 +5472,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>72</v>
@@ -5316,13 +5487,13 @@
         <v>72</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5373,13 +5544,13 @@
         <v>72</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>72</v>
@@ -5390,10 +5561,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5401,10 +5572,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
@@ -5416,13 +5587,13 @@
         <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5473,13 +5644,13 @@
         <v>72</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>72</v>
@@ -5490,10 +5661,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5504,7 +5675,7 @@
         <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
@@ -5516,13 +5687,13 @@
         <v>72</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5573,13 +5744,13 @@
         <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>72</v>
@@ -5590,10 +5761,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5604,7 +5775,7 @@
         <v>73</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>72</v>
@@ -5616,13 +5787,13 @@
         <v>72</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5673,13 +5844,13 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>72</v>
@@ -5690,10 +5861,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5701,10 +5872,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>72</v>
@@ -5716,13 +5887,13 @@
         <v>72</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5773,27 +5944,27 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5804,7 +5975,7 @@
         <v>73</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>72</v>
@@ -5816,13 +5987,13 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5873,13 +6044,13 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>188</v>
+        <v>87</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>72</v>
@@ -5890,21 +6061,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>72</v>
@@ -5916,15 +6087,17 @@
         <v>72</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>72</v>
@@ -5961,71 +6134,75 @@
         <v>72</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>190</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>72</v>
       </c>
@@ -6073,38 +6250,38 @@
         <v>72</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>72</v>
@@ -6116,17 +6293,15 @@
         <v>72</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>72</v>
@@ -6163,75 +6338,71 @@
         <v>72</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>96</v>
+        <v>209</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>72</v>
       </c>
@@ -6279,27 +6450,27 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>104</v>
+        <v>212</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6310,7 +6481,7 @@
         <v>73</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>72</v>
@@ -6322,13 +6493,13 @@
         <v>72</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6379,27 +6550,27 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6410,7 +6581,7 @@
         <v>73</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>72</v>
@@ -6422,13 +6593,13 @@
         <v>72</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>198</v>
+        <v>86</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6479,13 +6650,13 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>197</v>
+        <v>87</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>72</v>
@@ -6496,21 +6667,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>72</v>
@@ -6522,15 +6693,17 @@
         <v>72</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>200</v>
+        <v>91</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>72</v>
@@ -6567,71 +6740,75 @@
         <v>72</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>199</v>
+        <v>97</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>72</v>
       </c>
@@ -6679,27 +6856,27 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6710,7 +6887,7 @@
         <v>73</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>72</v>
@@ -6722,13 +6899,13 @@
         <v>72</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>85</v>
+        <v>223</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -6779,13 +6956,13 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>86</v>
+        <v>221</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>72</v>
@@ -6796,21 +6973,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>72</v>
@@ -6822,17 +6999,15 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>90</v>
+        <v>225</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>72</v>
@@ -6869,75 +7044,71 @@
         <v>72</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>72</v>
       </c>
@@ -6985,27 +7156,27 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7016,7 +7187,7 @@
         <v>73</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>72</v>
@@ -7028,13 +7199,13 @@
         <v>72</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>207</v>
+        <v>112</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7085,13 +7256,13 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>72</v>
@@ -7102,10 +7273,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7116,7 +7287,7 @@
         <v>73</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>72</v>
@@ -7128,13 +7299,13 @@
         <v>72</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7185,13 +7356,13 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>72</v>
@@ -7202,10 +7373,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7213,10 +7384,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>72</v>
@@ -7228,13 +7399,13 @@
         <v>72</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7285,27 +7456,27 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7316,7 +7487,7 @@
         <v>73</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>72</v>
@@ -7328,13 +7499,13 @@
         <v>72</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>83</v>
+        <v>240</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>84</v>
+        <v>241</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7385,13 +7556,13 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>72</v>
@@ -7402,21 +7573,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>72</v>
@@ -7428,17 +7599,15 @@
         <v>72</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>90</v>
+        <v>244</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>72</v>
@@ -7475,75 +7644,71 @@
         <v>72</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>101</v>
+        <v>247</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>72</v>
       </c>
@@ -7591,27 +7756,27 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7619,10 +7784,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>72</v>
@@ -7634,13 +7799,13 @@
         <v>72</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -7691,13 +7856,13 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>216</v>
+        <v>87</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>72</v>
@@ -7708,21 +7873,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>72</v>
@@ -7734,15 +7899,17 @@
         <v>72</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>220</v>
+        <v>91</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>72</v>
@@ -7779,71 +7946,75 @@
         <v>72</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>219</v>
+        <v>97</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>72</v>
       </c>
@@ -7891,27 +8062,27 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -7922,7 +8093,7 @@
         <v>73</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>72</v>
@@ -7934,13 +8105,13 @@
         <v>72</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -7991,13 +8162,13 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>72</v>
@@ -8008,10 +8179,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8022,7 +8193,7 @@
         <v>73</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>72</v>
@@ -8034,13 +8205,13 @@
         <v>72</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8091,18 +8262,924 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareContacts.xlsx
+++ b/StructureDefinition-SEEHDSLMCareContacts.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
